--- a/app/static/templates/LGD.xlsx
+++ b/app/static/templates/LGD.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Collateral Config" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Instructions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +29,90 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00334155"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001e293b"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A3C5E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F7FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E8F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAFAFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -42,12 +120,151 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="0094A3B8"/>
+      </left>
+      <right style="thin">
+        <color rgb="0094A3B8"/>
+      </right>
+      <top style="thin">
+        <color rgb="0094A3B8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001A3C5E"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0094A3B8"/>
+      </left>
+      <right style="thin">
+        <color rgb="0094A3B8"/>
+      </right>
+      <top style="thin">
+        <color rgb="0094A3B8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0094A3B8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="0094A3B8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="0094A3B8"/>
+      </right>
+      <top style="thin">
+        <color rgb="0094A3B8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="0094A3B8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0094A3B8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="0094A3B8"/>
+      </right>
+      <top style="thin">
+        <color rgb="0094A3B8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0094A3B8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -410,35 +627,933 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="0016A34A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Customer ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Loan ID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Outstanding Amount</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Effective Interest Rate (EIR)</t>
         </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Motor Vehicle</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cash Deposit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Corporate Guarantee</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>LN-2025-0001</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>490000</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>350000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>LN-2025-0002</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>748000</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CUST-002</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>LN-2025-0003</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>CUST-003</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>LN-2025-0004</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1060000</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>600000</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>180000</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>CUST-003</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>LN-2025-0005</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>860000</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>200000</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>CUST-004</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>LN-2025-0006</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>900000</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>LN-2025-0007</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>425000</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>LN-2025-0008</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>980000</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>750000</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>CUST-006</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>LN-2025-0009</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>300000</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>CUST-007</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>LN-2025-0010</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>630000</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>200000</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0016A34A"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Collateral Configuration — Important Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>What are the collateral columns?</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Columns E onward (Real Estate, Motor Vehicle …) represent the fair value of collateral pledged against each loan.  Each column name must be an exact, case-sensitive match to a Collateral Type name configured in your workspace (Workspace → Admin → Collateral Types).</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr"/>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>How to configure Collateral Types</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Navigate to Workspace → Admin → Collateral Types and create each category your portfolio uses.  The 'Name' field you enter there must match the column header in this file exactly.</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr"/>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>What is Haircut?</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>A percentage reduction applied to the collateral fair value to account for liquidation costs, market discounts, and forced-sale risk.  E.g. a 20 % haircut on KES 1 000 000 gives KES 800 000 recoverable before discounting.</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>What is Time to Realise?</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>The expected number of months to liquidate this collateral type.  Longer realisation periods reduce present value because of the time-value-of-money discount applied.</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Discount formula</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>For each collateral type:   Discounted Value = Fair Value × (1 − Haircut) × (1 + EIR) ^ (−Time_to_Realise)   where EIR is the loan's effective interest rate (column D).</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr"/>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>What if a collateral column is unrecognised?</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Validation error EC-02 blocks the run.  Either remove the column or add the collateral type in the admin screen so the system knows its haircut and time-to-realise values.</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>What if a loan has no collateral of a particular type?</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Enter 0 (zero).  Blank cells are treated as 0 but may trigger a validation warning.  Do not delete the column — all configured collateral type columns must be present.</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Example collateral types and typical IFRS 9 parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Collateral Type Name</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Typical Haircut %</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Typical Time to Realise (months)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>20 %</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Motor Vehicle</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>35 %</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Cash Deposit</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>0 %</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Corporate Guarantee</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>15 %</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Government Securities</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>5 %</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Equipment / Machinery</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>40 %</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0016A34A"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Loss Given Default (LGD) — Upload Guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Upload one LGD file per run (single workbook, 25 MB max).  Each row represents one active loan.  Collateral column names must exactly match the Collateral Types configured in your workspace.  See the 'Collateral Config' sheet in this workbook for detailed guidance.</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="n"/>
+      <c r="C2" s="18" t="n"/>
+      <c r="D2" s="18" t="n"/>
+      <c r="E2" s="18" t="n"/>
+      <c r="F2" s="19" t="n"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Column Name</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Allowed Values</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>Business Rule</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>Customer ID</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>Any non-empty string</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>A customer may have multiple loans.  Used for proportional collateral allocation: each loan's share of a customer's total collateral = Outstanding Amount / Total Customer Outstanding.</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>Loan ID</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>Unique per row</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>Must be unique within this file.  Primary key for LGD results.</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>LN-2025-0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>Outstanding Amount</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>≥ 0</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>Current outstanding principal balance.  Used to weight collateral allocation across loans belonging to the same customer.</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>490000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>Effective Interest Rate (EIR)</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>0 – 1  (decimal fraction)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>Annual EIR expressed as a decimal, e.g. enter 0.14 for 14 %.  Used as the discount rate in the collateral present-value formula (EC-05: must be 0 – 1).</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>[Collateral Type Name]</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>Yes*</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>≥ 0</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>*One column per configured Collateral Type.  Column name must be an exact match (EC-02).  Enter 0 if no collateral of this type is pledged for the loan.  Amount represents fair value before haircut.</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>350000.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Collateral discount formula (applied per type per loan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Discounted Value = Fair Value  ×  (1 − Haircut)  ×  (1 + EIR) ^ (−Time_to_Realise_months)</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="19" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  where:  Haircut and Time_to_Realise come from Workspace → Admin → Collateral Types.</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="n"/>
+      <c r="C13" s="18" t="n"/>
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="19" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          EIR comes from column D of this file.</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="19" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="25" t="inlineStr"/>
+      <c r="B15" s="18" t="n"/>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="19" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  The sum of discounted values across all collateral types = LGD recovery for that loan.</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="19" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  LGD % = 1 − (Recovery Amount / Outstanding Amount)  [capped at 0 % – 100 %].</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="19" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A15:F15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>